--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110087</v>
+        <v>110090</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110090</v>
+        <v>110091</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136189253</v>
       </c>
       <c r="B4" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136189256</v>
       </c>
       <c r="B5" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136189259</v>
       </c>
       <c r="B6" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136189260</v>
       </c>
       <c r="B7" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>136189263</v>
       </c>
       <c r="B8" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136189265</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>136189266</v>
       </c>
       <c r="B10" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136189268</v>
       </c>
       <c r="B11" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>136189270</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>136189272</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>136189274</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136189277</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>136189278</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136189279</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>136189267</v>
       </c>
       <c r="B18" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110091</v>
+        <v>110096</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32276-2026 artfynd.xlsx
+++ b/artfynd/A 32276-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136189262</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>136189248</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>136189249</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>136189251</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>136189252</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136189258</v>
       </c>
       <c r="B23" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>136189250</v>
       </c>
       <c r="B24" t="n">
-        <v>110096</v>
+        <v>110098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
